--- a/Productos Vta.xlsx
+++ b/Productos Vta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7286b9d7ec8af54a/Proyectos/ArmoniaShop-Mila/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{F5D12DB3-C7FE-456B-8358-C45036D5C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1B3883E-6563-462C-AAE4-984B7E9FC467}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{F5D12DB3-C7FE-456B-8358-C45036D5C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{862ABE9D-C459-4C4D-AF23-BB352C6A76C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61B29878-444D-407E-B9CF-CAB5D668DAC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61B29878-444D-407E-B9CF-CAB5D668DAC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>nombre</t>
   </si>
@@ -285,9 +288,6 @@
     <t>Juego 4 Vasos Murano 500Ml Morado.jpg</t>
   </si>
   <si>
-    <t>Licuadora (con detalle).jpg</t>
-  </si>
-  <si>
     <t>Perfume para dama y caballero de bolsillo.jpg</t>
   </si>
   <si>
@@ -394,9 +394,6 @@
   </si>
   <si>
     <t>src/assets/img/varios/Juego 4 Vasos Murano 500Ml Morado.jpg</t>
-  </si>
-  <si>
-    <t>src/assets/img/varios/Licuadora (con detalle).jpg</t>
   </si>
   <si>
     <t>src/assets/img/varios/Perfume para dama y caballero de bolsillo.jpg</t>
@@ -477,8 +474,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2556B951-D96C-494D-89A2-50487A4B6F9B}" name="Tabla1" displayName="Tabla1" ref="A1:D48" totalsRowShown="0">
-  <autoFilter ref="A1:D48" xr:uid="{2556B951-D96C-494D-89A2-50487A4B6F9B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2556B951-D96C-494D-89A2-50487A4B6F9B}" name="Tabla1" displayName="Tabla1" ref="A1:D47" totalsRowShown="0">
+  <autoFilter ref="A1:D47" xr:uid="{2556B951-D96C-494D-89A2-50487A4B6F9B}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5839851F-787E-4AB1-A956-3228047024C8}" name="nombre"/>
     <tableColumn id="2" xr3:uid="{7C206729-8A6D-4CB6-B068-C81B7AC90F04}" name="descripcion"/>
@@ -490,9 +487,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,7 +527,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -636,7 +633,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -778,7 +775,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -786,16 +783,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B048D7B0-20BA-436E-B5AC-8FFFA8D40E09}">
-  <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="62.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -809,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -823,7 +820,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -837,7 +834,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -851,7 +848,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -865,7 +862,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -879,7 +876,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -893,7 +890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -907,7 +904,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -921,7 +918,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -935,7 +932,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -949,7 +946,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
@@ -963,7 +960,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
@@ -977,7 +974,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
@@ -991,7 +988,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1005,7 +1002,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -1019,7 +1016,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
@@ -1033,7 +1030,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>11</v>
       </c>
@@ -1047,7 +1044,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1061,7 +1058,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -1075,7 +1072,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
@@ -1089,7 +1086,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>23</v>
       </c>
@@ -1103,7 +1100,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
@@ -1117,7 +1114,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
@@ -1131,7 +1128,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
@@ -1145,7 +1142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
@@ -1159,163 +1156,163 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="4">
         <v>40</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4">
         <v>99.9</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4">
         <v>59.9</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4">
         <v>59.9</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="4">
         <v>69.900000000000006</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4">
         <v>69.900000000000006</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4">
         <v>89.9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="4">
         <v>99.9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4">
         <v>225</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="4">
         <v>89.9</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="4">
         <v>89.9</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="4">
         <v>99.9</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="4">
         <v>49.9</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>79</v>
       </c>
@@ -1324,34 +1321,34 @@
         <v>150</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="4">
         <v>150</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="4">
         <v>150</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>80</v>
       </c>
@@ -1360,10 +1357,10 @@
         <v>180</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>81</v>
       </c>
@@ -1372,34 +1369,34 @@
         <v>99</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="4">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="4">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>84</v>
       </c>
@@ -1408,19 +1405,7 @@
         <v>20</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="4">
-        <v>20</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
